--- a/inputs/column_mappings.xlsx
+++ b/inputs/column_mappings.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,16 +449,6 @@
           <t>status</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>cast_note</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
